--- a/data/trans_orig/Predimed-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed)</t>
+          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed) (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 6,56</t>
+          <t>6,19; 6,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 6,28</t>
+          <t>5,99; 6,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 6,34</t>
+          <t>6,12; 6,36</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 6,58</t>
+          <t>6,24; 6,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 6,99</t>
+          <t>6,41; 7,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 6,75</t>
+          <t>6,37; 6,75</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 6,87</t>
+          <t>6,41; 6,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,08</t>
+          <t>6,77; 7,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 6,93</t>
+          <t>6,63; 6,93</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 6,57</t>
+          <t>6,33; 6,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 6,82</t>
+          <t>6,44; 6,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,68</t>
+          <t>6,42; 6,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Estudios-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,37</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,13</t>
+          <t>6,07</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,18</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 6,56</t>
+          <t>6,16; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 6,28</t>
+          <t>5,94; 6,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 6,36</t>
+          <t>6,08; 6,3</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>6,25</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>6,38</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>6,32</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 6,59</t>
+          <t>6,13; 6,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 7,01</t>
+          <t>6,29; 6,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 6,75</t>
+          <t>6,24; 6,39</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>6,73</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>6,91</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>6,82</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 6,87</t>
+          <t>6,53; 6,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,09</t>
+          <t>6,76; 7,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 6,93</t>
+          <t>6,69; 6,95</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>6,4</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 6,57</t>
+          <t>6,28; 6,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 6,83</t>
+          <t>6,35; 6,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,69</t>
+          <t>6,34; 6,45</t>
         </is>
       </c>
     </row>
